--- a/ksoft_old/docs/fields_details/Item_Fields_Detail.xlsx
+++ b/ksoft_old/docs/fields_details/Item_Fields_Detail.xlsx
@@ -1156,13 +1156,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAF35DF0-2394-456F-A6B1-EE359C151BD4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02D88D8A-CCC9-4EF5-A85C-E347BBE0EB19}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D54DCEE3-276B-4B09-9F16-BCE37621ADD5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{687FF378-8D1F-4C41-99A0-30D33F600B86}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32A5B799-CA4B-475B-8348-F6AFCF3D3844}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5217ABAA-40BA-47F3-9C74-91EC1118D081}"/>
 </file>
--- a/ksoft_old/docs/fields_details/Item_Fields_Detail.xlsx
+++ b/ksoft_old/docs/fields_details/Item_Fields_Detail.xlsx
@@ -1156,13 +1156,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02D88D8A-CCC9-4EF5-A85C-E347BBE0EB19}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26A7AB65-37A2-4CCC-9B7B-AD6B99BF0805}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{687FF378-8D1F-4C41-99A0-30D33F600B86}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8D45CF9-F9BB-4D60-A974-AF9516CD582F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5217ABAA-40BA-47F3-9C74-91EC1118D081}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AD6185E-47EE-4182-8102-E3438DE6F82E}"/>
 </file>
--- a/ksoft_old/docs/fields_details/Item_Fields_Detail.xlsx
+++ b/ksoft_old/docs/fields_details/Item_Fields_Detail.xlsx
@@ -1156,13 +1156,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26A7AB65-37A2-4CCC-9B7B-AD6B99BF0805}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAF35DF0-2394-456F-A6B1-EE359C151BD4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8D45CF9-F9BB-4D60-A974-AF9516CD582F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D54DCEE3-276B-4B09-9F16-BCE37621ADD5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AD6185E-47EE-4182-8102-E3438DE6F82E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32A5B799-CA4B-475B-8348-F6AFCF3D3844}"/>
 </file>